--- a/Test Cases/Test Case For VWO.xlsx
+++ b/Test Cases/Test Case For VWO.xlsx
@@ -5,7 +5,7 @@
   <workbookPr defaultThemeVersion="164011"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\IDEAL\OneDrive\Pictures\SQA\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\IDEAL\OneDrive\Pictures\SQA\Projects\All Projects\1st Manual Project-VWO\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
@@ -24,7 +24,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="135" uniqueCount="109">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="137" uniqueCount="111">
   <si>
     <t>Test Case Template for Project</t>
   </si>
@@ -511,6 +511,12 @@
   <si>
     <t>It must be show "Sign Up" page</t>
   </si>
+  <si>
+    <t>verify the login page for both when the field is blank and submit button is clicked</t>
+  </si>
+  <si>
+    <t>TS_03</t>
+  </si>
 </sst>
 </file>
 
@@ -760,12 +766,6 @@
     <xf numFmtId="0" fontId="4" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
@@ -788,6 +788,12 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1087,11 +1093,11 @@
     <row r="2" spans="1:31" ht="15.75" thickBot="1"/>
     <row r="3" spans="1:31" s="2" customFormat="1" ht="54" customHeight="1" thickBot="1">
       <c r="A3" s="1"/>
-      <c r="B3" s="15" t="s">
+      <c r="B3" s="23" t="s">
         <v>0</v>
       </c>
-      <c r="C3" s="16"/>
-      <c r="D3" s="21"/>
+      <c r="C3" s="24"/>
+      <c r="D3" s="19"/>
       <c r="E3" s="11"/>
       <c r="F3" s="1"/>
       <c r="G3" s="1"/>
@@ -1125,10 +1131,10 @@
       <c r="B4" s="4" t="s">
         <v>1</v>
       </c>
-      <c r="C4" s="18" t="s">
+      <c r="C4" s="16" t="s">
         <v>20</v>
       </c>
-      <c r="D4" s="22"/>
+      <c r="D4" s="20"/>
       <c r="E4" s="12"/>
       <c r="F4" s="1"/>
       <c r="G4" s="1"/>
@@ -1156,13 +1162,13 @@
     </row>
     <row r="5" spans="1:31" ht="18.75" thickBot="1">
       <c r="A5" s="3"/>
-      <c r="B5" s="20" t="s">
+      <c r="B5" s="18" t="s">
         <v>2</v>
       </c>
-      <c r="C5" s="19" t="s">
+      <c r="C5" s="17" t="s">
         <v>22</v>
       </c>
-      <c r="D5" s="23"/>
+      <c r="D5" s="21"/>
       <c r="E5" s="13"/>
       <c r="F5" s="1"/>
       <c r="G5" s="1"/>
@@ -1488,7 +1494,7 @@
       <c r="A14" s="2" t="s">
         <v>23</v>
       </c>
-      <c r="B14" s="17" t="s">
+      <c r="B14" s="15" t="s">
         <v>19</v>
       </c>
       <c r="C14" s="10" t="s">
@@ -1541,7 +1547,7 @@
       <c r="A15" s="8" t="s">
         <v>33</v>
       </c>
-      <c r="B15" s="17" t="s">
+      <c r="B15" s="15" t="s">
         <v>35</v>
       </c>
       <c r="C15" s="10" t="s">
@@ -1591,8 +1597,12 @@
       <c r="AE15" s="10"/>
     </row>
     <row r="16" spans="1:31" ht="52.5" thickBot="1">
-      <c r="A16" s="10"/>
-      <c r="B16" s="10"/>
+      <c r="A16" s="10" t="s">
+        <v>110</v>
+      </c>
+      <c r="B16" s="10" t="s">
+        <v>109</v>
+      </c>
       <c r="C16" s="10" t="s">
         <v>36</v>
       </c>
@@ -2305,7 +2315,7 @@
       <c r="B32" s="10"/>
       <c r="C32" s="10"/>
       <c r="D32" s="10"/>
-      <c r="E32" s="24"/>
+      <c r="E32" s="22"/>
       <c r="F32" s="10"/>
       <c r="G32" s="10"/>
       <c r="H32" s="10"/>
